--- a/artfynd/A 49457-2023 artfynd.xlsx
+++ b/artfynd/A 49457-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49457-2023 artfynd.xlsx
+++ b/artfynd/A 49457-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109975020</v>
+        <v>109975011</v>
       </c>
       <c r="B4" t="n">
-        <v>95511</v>
+        <v>95519</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,33 +925,24 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221944</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Grytsjöskogen, S om Norrlången, Srm</t>
@@ -1032,123 +1023,6 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>109975011</v>
-      </c>
-      <c r="B5" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Grytsjöskogen, S om Norrlången, Srm</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>594659.2612465108</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6567249.825610028</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Eskilstuna</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Ärla</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2023-06-06</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2023-06-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Myrkant</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Håkan Gustafson</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Håkan Gustafson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
